--- a/data/trans_dic/IP43-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP43-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones</t>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 21,92</t>
+          <t>8,23; 22,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 24,1</t>
+          <t>8,61; 24,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,52; 33,27</t>
+          <t>16,0; 34,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 25,38</t>
+          <t>9,47; 25,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 26,64</t>
+          <t>13,76; 26,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,12; 22,47</t>
+          <t>11,42; 22,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,94</t>
+          <t>8,81; 19,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 26,75</t>
+          <t>15,23; 27,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 21,74</t>
+          <t>13,31; 21,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 19,14</t>
+          <t>6,87; 19,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,9</t>
+          <t>11,07; 25,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 14,72</t>
+          <t>4,0; 15,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,99</t>
+          <t>2,68; 11,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,85</t>
+          <t>6,6; 14,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,6</t>
+          <t>7,63; 15,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,72; 90,13</t>
+          <t>68,22; 89,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 47,3</t>
+          <t>23,15; 46,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68,2; 87,91</t>
+          <t>68,13; 88,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 41,07</t>
+          <t>19,83; 42,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,33; 86,55</t>
+          <t>72,55; 87,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,69; 40,03</t>
+          <t>23,03; 39,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,27</t>
+          <t>1,42; 12,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,98</t>
+          <t>1,31; 7,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,04</t>
+          <t>1,97; 8,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,41</t>
+          <t>0,57; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,98</t>
+          <t>2,32; 8,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,81</t>
+          <t>1,48; 6,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,72</t>
+          <t>2,68; 7,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,97</t>
+          <t>1,4; 4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,55; 59,88</t>
+          <t>47,52; 60,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,25; 33,61</t>
+          <t>23,46; 34,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,18</t>
+          <t>45,37; 57,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,34; 33,16</t>
+          <t>22,15; 33,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,06; 57,08</t>
+          <t>47,74; 56,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,32; 31,71</t>
+          <t>24,22; 31,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,2</t>
+          <t>20,46; 25,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,33</t>
+          <t>10,69; 14,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20,9; 25,8</t>
+          <t>20,92; 25,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,47</t>
+          <t>9,68; 13,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,44; 24,93</t>
+          <t>21,44; 25,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,62; 13,23</t>
+          <t>10,61; 13,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8665</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15251</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10747</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23191</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19412</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4593; 12523</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4937; 13987</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10179; 21768</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6101; 16368</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16440; 31625</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13915; 27350</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14073</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22415</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36488</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>9115; 20307</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16622; 30166</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3210</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28297; 46662</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3798</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4825</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3848</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3604</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9167</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16055</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18054</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5284; 15217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8521; 19616</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3287; 12508</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2177; 9384</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10502; 23613</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>12069; 25096</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>34984</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14924</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36467</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71451</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>28396</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29426; 38716</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10057; 20004</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31411; 40584</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9190; 19757</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>64744; 77640</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>20681; 35247</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3740</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2616</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>818; 7253</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2349</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1467; 8395</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6915</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2729; 11125</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>780; 7549</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3384; 12200</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2132; 9589</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7627; 20037</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3926; 14013</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>88282</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>46338</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>85976</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>46903</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>174257</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>93241</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>77680; 98531</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>38513; 56616</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>76153; 97025</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>37840; 56775</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>158181; 187510</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>81138; 107014</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>160932</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>86819</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>174370</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>85333</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>335301</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>172152</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>144375; 180570</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>75310; 103074</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>156126; 193207</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>72087; 100281</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>311265; 363281</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>153793; 193495</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>